--- a/integration_tests/tests/assets/integration_test/input_data/excel_data.xlsx
+++ b/integration_tests/tests/assets/integration_test/input_data/excel_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrick/RustroverProjects/PhenoXtrackt/tests/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/patrick/RustroverProjects/PhenoXtrackt/integration_tests/tests/assets/integration_test/input_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B26DBE9-742B-B14A-A145-3D72CC4CE605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0659096-B0FA-A044-9AF4-D5434F2828A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17120" xr2:uid="{B5F6743A-E238-884E-8FE8-3F2B7107E66E}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17120" activeTab="2" xr2:uid="{B5F6743A-E238-884E-8FE8-3F2B7107E66E}"/>
   </bookViews>
   <sheets>
     <sheet name="basic info" sheetId="1" r:id="rId1"/>
@@ -145,12 +145,6 @@
     <t>Phenotypic Features 5</t>
   </si>
   <si>
-    <t>asthma</t>
-  </si>
-  <si>
-    <t>macrocephaly</t>
-  </si>
-  <si>
     <t>short stature</t>
   </si>
   <si>
@@ -188,6 +182,12 @@
   </si>
   <si>
     <t>P007</t>
+  </si>
+  <si>
+    <t>Arachnodactyly</t>
+  </si>
+  <si>
+    <t>arachnodactyly</t>
   </si>
 </sst>
 </file>
@@ -620,13 +620,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>11</v>
@@ -637,7 +637,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -654,7 +654,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -677,7 +677,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
         <v>3</v>
@@ -719,13 +719,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7">
         <v>1432</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" s="5">
         <v>34414</v>
@@ -832,7 +832,7 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
         <v>28</v>
@@ -904,7 +904,7 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -918,7 +918,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.2">
@@ -926,13 +926,13 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -940,7 +940,7 @@
         <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
